--- a/call-list/私立高校_架電リスト_北海道.xlsx
+++ b/call-list/私立高校_架電リスト_北海道.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$L$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$59</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,15 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
+      <color rgb="00595959"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
@@ -69,7 +78,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +93,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,24 +142,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -143,12 +167,27 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -534,21 +573,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,7 +603,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出典：学校ネット 私立高校検索結果（ご提供の貼り付けデータ）。電話番号は元データに記載がないため空欄です。黄色の列に入力してください。</t>
+          <t>出典：学校ネット 私立高校検索結果（ご提供の貼り付けデータ）。電話番号は2026年10月にWeb検索で調査（出典・確度はM〜N列）。架電前に「確度：中・低」の番号は念のためご確認ください。</t>
         </is>
       </c>
     </row>
@@ -593,37 +635,52 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>番号の確度</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>学科</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>架電日</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>架電結果</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>次回連絡日</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>電話番号の補足</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>電話番号の出典</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>学校情報ページ</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>架電日</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>担当者</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>架電結果</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>次回連絡日</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>メモ</t>
         </is>
       </c>
     </row>
@@ -646,15 +703,19 @@
           <t>旭川志峯高等学校</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0166-48-1221</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H5" s="8" t="n"/>
@@ -666,6 +727,21 @@
       </c>
       <c r="K5" s="8" t="n"/>
       <c r="L5" s="9" t="n"/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>旧称は旭川大学高校。ハローワーク旭川の名簿（R7.6）とJS日本の学校の番号が一致</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>https://jsite.mhlw.go.jp/hokkaido-hellowork/content/contents/002280302.pdf ; https://school.js88.com/scl_h/22052950</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -686,15 +762,19 @@
           <t>旭川実業高等学校</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0166-51-1246</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H6" s="8" t="n"/>
@@ -706,6 +786,21 @@
       </c>
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="9" t="n"/>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>ハローワーク名簿とJS日本の学校・みんなの高校情報の番号が一致</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>https://jsite.mhlw.go.jp/hokkaido-hellowork/content/contents/002280302.pdf ; https://school.js88.com/scl_h/22052940</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -726,15 +821,19 @@
           <t>旭川藤星高等学校</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0166-51-8125</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H7" s="8" t="n"/>
@@ -746,6 +845,21 @@
       </c>
       <c r="K7" s="8" t="n"/>
       <c r="L7" s="9" t="n"/>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校のみで確認。公式サイトは asahikawa-tosei.jp</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052920</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -766,15 +880,19 @@
           <t>旭川明成高等学校</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>0166-51-3220</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>総合学科</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H8" s="8" t="n"/>
@@ -786,6 +904,21 @@
       </c>
       <c r="K8" s="8" t="n"/>
       <c r="L8" s="9" t="n"/>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>ハローワーク名簿とJS日本の学校の番号が一致</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>https://jsite.mhlw.go.jp/hokkaido-hellowork/content/contents/002280302.pdf ; https://school.js88.com/scl_h/22053120</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -806,15 +939,19 @@
           <t>旭川龍谷高等学校</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>0166-39-2700</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H9" s="8" t="n"/>
@@ -826,6 +963,21 @@
       </c>
       <c r="K9" s="8" t="n"/>
       <c r="L9" s="9" t="n"/>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校と道私学協会の資料（2023）の番号が一致</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052930 ; https://www.doshigaku.jp/pdf/2023_transfe_10.pdf</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -846,15 +998,19 @@
           <t>遺愛女子高等学校（青山学院大学教育提携校）</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>0138-51-0418</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H10" s="8" t="n"/>
@@ -866,6 +1022,21 @@
       </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="9" t="n"/>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>公式パンフレットで確認。学院の代表番号（中学校と共通）</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>https://www.iaijoshi-h.ed.jp/wp-content/uploads/2022/07/2023遺愛女子高校パンフレット.pdf</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -886,15 +1057,19 @@
           <t>池上学院高等学校</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>011-811-5297</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H11" s="8" t="n"/>
@@ -906,6 +1081,21 @@
       </c>
       <c r="K11" s="8" t="n"/>
       <c r="L11" s="9" t="n"/>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>通信制・札幌本校の番号。入学相談用フリーダイヤル0120-195-315の記載もあり</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>https://www.minkou.jp/hischool/school/330/</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -926,15 +1116,19 @@
           <t>小樽双葉高等学校</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>0134-32-1828</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H12" s="8" t="n"/>
@@ -946,6 +1140,21 @@
       </c>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="9" t="n"/>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校と道私学協会の資料の番号が一致。通信制課程の職員室は0134-31-3100</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052880 ; https://www.doshigaku.jp/pdf/2023_transfe_10.pdf</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -966,15 +1175,19 @@
           <t>小樽明峰高等学校</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>0134-22-7755</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H13" s="8" t="n"/>
@@ -986,6 +1199,21 @@
       </c>
       <c r="K13" s="8" t="n"/>
       <c r="L13" s="9" t="n"/>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校と札幌市中学校の資料の番号が一致</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052890/ ; https://www16.sapporo-c.ed.jp/sakaeminami-j/attach/get2/4692/0</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1006,15 +1234,19 @@
           <t>帯広大谷高等学校</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>0155-33-5811</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H14" s="8" t="n"/>
@@ -1026,6 +1258,21 @@
       </c>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="9" t="n"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>2018年の高文連資料のみで確認。最新かは未確認</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>https://www.koubunren-volunteer.hokkaido-c.ed.jp/wysiwyg/file/download/1/16</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1046,15 +1293,19 @@
           <t>帯広北高等学校</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>0155-47-0121</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H15" s="8" t="n"/>
@@ -1066,6 +1317,21 @@
       </c>
       <c r="K15" s="8" t="n"/>
       <c r="L15" s="9" t="n"/>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校とみんなの高校情報の番号が一致</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053070 ; https://www.minkou.jp/hischool/school/1042/</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1086,15 +1352,19 @@
           <t>海星学院高等学校</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0143-46-8888</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H16" s="8" t="n"/>
@@ -1106,6 +1376,21 @@
       </c>
       <c r="K16" s="8" t="n"/>
       <c r="L16" s="9" t="n"/>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校のみで確認</t>
+        </is>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053040</t>
+        </is>
+      </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1126,15 +1411,19 @@
           <t>北見藤高等学校</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0157-23-3212</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H17" s="8" t="n"/>
@@ -1146,6 +1435,21 @@
       </c>
       <c r="K17" s="8" t="n"/>
       <c r="L17" s="9" t="n"/>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校とYahoo!マップで一致</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052980 ; https://map.yahoo.co.jp/v3/place/F1bCf-OH6f6</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1166,15 +1470,19 @@
           <t>クラーク記念国際高等学校</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>0164-24-2001</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H18" s="8" t="n"/>
@@ -1186,6 +1494,21 @@
       </c>
       <c r="K18" s="8" t="n"/>
       <c r="L18" s="9" t="n"/>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>深川市の本校の番号。全国にキャンパスあり</t>
+        </is>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>https://www.minkou.jp/hischool/school/1635/</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1206,15 +1529,19 @@
           <t>駒澤大学附属苫小牧高等学校</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>0144-32-6291</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H19" s="8" t="n"/>
@@ -1226,6 +1553,21 @@
       </c>
       <c r="K19" s="8" t="n"/>
       <c r="L19" s="9" t="n"/>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校のみで確認</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053010</t>
+        </is>
+      </c>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1246,15 +1588,19 @@
           <t>札幌大谷高等学校</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>011-731-2451</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H20" s="8" t="n"/>
@@ -1266,6 +1612,21 @@
       </c>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="9" t="n"/>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>札幌市の一覧とJS日本の学校で一致。中学校と共通</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>https://www.city.sapporo.jp/higashi/about/ins_school.html ; https://school.js88.com/scl_h/22052680</t>
+        </is>
+      </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1286,15 +1647,19 @@
           <t>札幌光星高等学校</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>011-711-7161</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H21" s="8" t="n"/>
@@ -1306,6 +1671,21 @@
       </c>
       <c r="K21" s="8" t="n"/>
       <c r="L21" s="9" t="n"/>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>公式資料に「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sapporokosei.ac.jp/common/img/content/content_20260428_165448.pdf</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1326,15 +1706,19 @@
           <t>札幌新陽高等学校</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>011-821-6161</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H22" s="8" t="n"/>
@@ -1346,6 +1730,21 @@
       </c>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="9" t="n"/>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>札幌市の一覧とJS日本の学校で一致</t>
+        </is>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>https://www.city.sapporo.jp/minami/shisetsu/sonota.html ; https://school.js88.com/scl_h/22052720</t>
+        </is>
+      </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1366,15 +1765,15 @@
           <t>札幌自由が丘学園三和高等学校</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>要調査</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H23" s="8" t="n"/>
@@ -1386,6 +1785,21 @@
       </c>
       <c r="K23" s="8" t="n"/>
       <c r="L23" s="9" t="n"/>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>和寒本校の番号を特定できず。候補：011-792-1468（公式では札幌学習センター）／011-743-1267。校名変更の可能性あり</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>https://sanwa71.sakura.ne.jp/contact/ ; https://www.mapion.co.jp/phonebook/M11004/01464/ILSP0000041214_ipclm/</t>
+        </is>
+      </c>
+      <c r="O23" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1406,15 +1820,19 @@
           <t>札幌静修高等学校</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>011-521-0234</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H24" s="8" t="n"/>
@@ -1426,6 +1844,21 @@
       </c>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="9" t="n"/>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校のみで確認</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052690</t>
+        </is>
+      </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1446,15 +1879,19 @@
           <t>札幌創成高等学校</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>011-726-1578</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H25" s="8" t="n"/>
@@ -1466,6 +1903,21 @@
       </c>
       <c r="K25" s="8" t="n"/>
       <c r="L25" s="9" t="n"/>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>道私学協会の資料と札幌市中学校の配布資料で一致</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>https://www.doshigaku.jp/pdf/2023_transfe_10.pdf ; https://school.js88.com/scl_h/22049910</t>
+        </is>
+      </c>
+      <c r="O25" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1486,15 +1938,19 @@
           <t>札幌第一高等学校</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>011-851-9361</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H26" s="8" t="n"/>
@@ -1506,6 +1962,21 @@
       </c>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="9" t="n"/>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで「代表」と確認。入試事務局は011-851-6729</t>
+        </is>
+      </c>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kibou.ac.jp/daiichi/introduction/access/</t>
+        </is>
+      </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1526,15 +1997,19 @@
           <t>札幌日本大学高等学校</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>011-375-2611</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H27" s="8" t="n"/>
@@ -1546,6 +2021,21 @@
       </c>
       <c r="K27" s="8" t="n"/>
       <c r="L27" s="9" t="n"/>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>複数資料で一致。中高併設</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053100</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1566,15 +2056,19 @@
           <t>札幌北斗高等学校</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>011-711-6121</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H28" s="8" t="n"/>
@@ -1586,6 +2080,21 @@
       </c>
       <c r="K28" s="8" t="n"/>
       <c r="L28" s="9" t="n"/>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>札幌市東区の学校一覧と地図サイトで一致</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr">
+        <is>
+          <t>https://www.city.sapporo.jp/higashi/about/ins_school.html</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1606,15 +2115,19 @@
           <t>札幌山の手高等学校</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>011-611-7301</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H29" s="8" t="n"/>
@@ -1626,6 +2139,21 @@
       </c>
       <c r="K29" s="8" t="n"/>
       <c r="L29" s="9" t="n"/>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。札幌市立中学校の配布資料と一致</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052710</t>
+        </is>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1646,15 +2174,19 @@
           <t>札幌龍谷学園高等学校</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>011-631-4386</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H30" s="8" t="n"/>
@@ -1666,6 +2198,21 @@
       </c>
       <c r="K30" s="8" t="n"/>
       <c r="L30" s="9" t="n"/>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>札幌市立中学校の配布チラシで確認。公式サイトでは未確認</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>https://www16.sapporo-c.ed.jp/kiyota-j/attach/get2/2208/0</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1686,15 +2233,19 @@
           <t>白樺学園高等学校</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>0155-62-7411</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H31" s="8" t="n"/>
@@ -1706,6 +2257,21 @@
       </c>
       <c r="K31" s="8" t="n"/>
       <c r="L31" s="9" t="n"/>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>中高併設</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053060</t>
+        </is>
+      </c>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1726,15 +2292,19 @@
           <t>星槎国際高等学校</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>0124-24-6101</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H32" s="8" t="n"/>
@@ -1746,6 +2316,21 @@
       </c>
       <c r="K32" s="8" t="n"/>
       <c r="L32" s="9" t="n"/>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>芦別の本部校の番号（公式サイト）。全国にキャンパスあり</t>
+        </is>
+      </c>
+      <c r="N32" s="11" t="inlineStr">
+        <is>
+          <t>https://seisa.ed.jp/ashibetsu/access/</t>
+        </is>
+      </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1766,15 +2351,19 @@
           <t>清尚学院高等学校</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>0138-41-6584</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>専門学科</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H33" s="8" t="n"/>
@@ -1786,6 +2375,21 @@
       </c>
       <c r="K33" s="8" t="n"/>
       <c r="L33" s="9" t="n"/>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校のみで確認</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052840</t>
+        </is>
+      </c>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1806,15 +2410,19 @@
           <t>東海大学付属札幌高等学校</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>011-571-5175</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H34" s="8" t="n"/>
@@ -1826,6 +2434,21 @@
       </c>
       <c r="K34" s="8" t="n"/>
       <c r="L34" s="9" t="n"/>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>複数資料で一致</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052760/</t>
+        </is>
+      </c>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1846,15 +2469,19 @@
           <t>苫小牧中央高等学校</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>0144-74-4200</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H35" s="8" t="n"/>
@@ -1866,6 +2493,21 @@
       </c>
       <c r="K35" s="8" t="n"/>
       <c r="L35" s="9" t="n"/>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>公式サイト：事務室。職員室は0144-74-4300</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>https://haragakuen.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -1886,15 +2528,19 @@
           <t>日本航空高等学校 北海道</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>0123-28-1155</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>専門学科</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H36" s="8" t="n"/>
@@ -1906,6 +2552,21 @@
       </c>
       <c r="K36" s="8" t="n"/>
       <c r="L36" s="9" t="n"/>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>千歳市の北海道キャンパスの番号。日本航空大学校とは別</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/34055718</t>
+        </is>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -1926,15 +2587,19 @@
           <t>函館大谷高等学校</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>0138-52-1834</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H37" s="8" t="n"/>
@@ -1946,6 +2611,21 @@
       </c>
       <c r="K37" s="8" t="n"/>
       <c r="L37" s="9" t="n"/>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校のみで確認</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052800/</t>
+        </is>
+      </c>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -1966,15 +2646,19 @@
           <t>函館大妻高等学校</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>0138-52-1890</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H38" s="8" t="n"/>
@@ -1986,6 +2670,21 @@
       </c>
       <c r="K38" s="8" t="n"/>
       <c r="L38" s="9" t="n"/>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>みんなの高校情報のみで確認</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr">
+        <is>
+          <t>https://www.minkou.jp/hischool/school/deviation/3622/?c=1</t>
+        </is>
+      </c>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2006,15 +2705,19 @@
           <t>函館白百合学園高等学校</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>0138-55-6682</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H39" s="8" t="n"/>
@@ -2026,6 +2729,21 @@
       </c>
       <c r="K39" s="8" t="n"/>
       <c r="L39" s="9" t="n"/>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表番号</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052830</t>
+        </is>
+      </c>
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2046,15 +2764,19 @@
           <t>函館大学付属柏稜高等学校</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>0138-51-1481</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H40" s="8" t="n"/>
@@ -2066,6 +2788,21 @@
       </c>
       <c r="K40" s="8" t="n"/>
       <c r="L40" s="9" t="n"/>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校とみんなの高校情報で一致</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052850</t>
+        </is>
+      </c>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2086,15 +2823,19 @@
           <t>函館大学付属有斗高等学校</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>0138-57-1381</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H41" s="8" t="n"/>
@@ -2106,6 +2847,21 @@
       </c>
       <c r="K41" s="8" t="n"/>
       <c r="L41" s="9" t="n"/>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>複数の進学情報サイトで一致</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052810</t>
+        </is>
+      </c>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2126,15 +2882,19 @@
           <t>函館ラ・サール高等学校</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>0138-52-0365</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H42" s="8" t="n"/>
@@ -2146,6 +2906,21 @@
       </c>
       <c r="K42" s="8" t="n"/>
       <c r="L42" s="9" t="n"/>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052860?page=6</t>
+        </is>
+      </c>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2166,15 +2941,19 @@
           <t>藤女子高等学校</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>011-707-5001</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H43" s="8" t="n"/>
@@ -2186,6 +2965,21 @@
       </c>
       <c r="K43" s="8" t="n"/>
       <c r="L43" s="9" t="n"/>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>公式の募集要項PDFと道私学協会の資料で一致</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fuji-gjshs.jp/20020/files/2026kou_youkou.pdf</t>
+        </is>
+      </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2206,15 +3000,19 @@
           <t>武修館高等学校</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>0154-47-3211</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H44" s="8" t="n"/>
@@ -2226,6 +3024,21 @@
       </c>
       <c r="K44" s="8" t="n"/>
       <c r="L44" s="9" t="n"/>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校とみんなの高校情報で一致。中学校は別番号（0154-47-3220）</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053090/</t>
+        </is>
+      </c>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2246,15 +3059,19 @@
           <t>北照高等学校</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>0134-32-0331</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H45" s="8" t="n"/>
@@ -2266,6 +3083,21 @@
       </c>
       <c r="K45" s="8" t="n"/>
       <c r="L45" s="9" t="n"/>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトと公式PDFで一致</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052870</t>
+        </is>
+      </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -2286,15 +3118,19 @@
           <t>北星学園女子高等学校</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>011-561-7153</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H46" s="8" t="n"/>
@@ -2306,6 +3142,21 @@
       </c>
       <c r="K46" s="8" t="n"/>
       <c r="L46" s="9" t="n"/>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>学校情報サイトと札幌市中学校の掲載資料で一致</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052670?page=9</t>
+        </is>
+      </c>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2326,15 +3177,19 @@
           <t>北星学園大学附属高等学校</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>011-897-2881</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H47" s="8" t="n"/>
@@ -2346,6 +3201,21 @@
       </c>
       <c r="K47" s="8" t="n"/>
       <c r="L47" s="9" t="n"/>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>JS日本の学校とみんなの高校情報で一致</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052660</t>
+        </is>
+      </c>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -2366,15 +3236,19 @@
           <t>北星学園余市高等学校</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>0135-23-2165</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H48" s="8" t="n"/>
@@ -2386,6 +3260,21 @@
       </c>
       <c r="K48" s="8" t="n"/>
       <c r="L48" s="9" t="n"/>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>公式PDF（2026年5月）では「事務室 0135-23-2166」の記載あり。要確認</t>
+        </is>
+      </c>
+      <c r="N48" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052900/</t>
+        </is>
+      </c>
+      <c r="O48" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2406,15 +3295,19 @@
           <t>北嶺高等学校</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>011-883-4651</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H49" s="8" t="n"/>
@@ -2426,6 +3319,21 @@
       </c>
       <c r="K49" s="8" t="n"/>
       <c r="L49" s="9" t="n"/>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053110 ; https://www.inter-edu.com/schools/school/321</t>
+        </is>
+      </c>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -2446,15 +3354,19 @@
           <t>北海学園札幌高等学校</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>011-841-1161</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H50" s="8" t="n"/>
@@ -2466,6 +3378,21 @@
       </c>
       <c r="K50" s="8" t="n"/>
       <c r="L50" s="9" t="n"/>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで「代表」と確認。北海高校・北海学園大学と同じ代表番号のため、学校名を伝えて取り次ぎを依頼</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hgs.ed.jp/about/index.html</t>
+        </is>
+      </c>
+      <c r="O50" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2486,15 +3413,19 @@
           <t>北海高等学校</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>011-841-1161</t>
+        </is>
+      </c>
+      <c r="F51" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H51" s="8" t="n"/>
@@ -2506,6 +3437,21 @@
       </c>
       <c r="K51" s="8" t="n"/>
       <c r="L51" s="9" t="n"/>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>北海学園の共通代表番号。学校名を伝えて取り次ぎを依頼</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052590 ; https://www.hokkai.ed.jp/sub/access.html</t>
+        </is>
+      </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -2526,15 +3472,19 @@
           <t>北海道大谷室蘭高等学校</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>0143-44-5641</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H52" s="8" t="n"/>
@@ -2546,6 +3496,21 @@
       </c>
       <c r="K52" s="8" t="n"/>
       <c r="L52" s="9" t="n"/>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>学校情報サイト1件のみで確認</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052990?page=6</t>
+        </is>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2566,15 +3531,19 @@
           <t>北海道科学大学高等学校</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>011-699-6987</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H53" s="8" t="n"/>
@@ -2586,6 +3555,21 @@
       </c>
       <c r="K53" s="8" t="n"/>
       <c r="L53" s="9" t="n"/>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>札幌市の一覧で確認。大学の番号とは別</t>
+        </is>
+      </c>
+      <c r="N53" s="11" t="inlineStr">
+        <is>
+          <t>https://www.city.sapporo.jp/teine/shisetsu/school.html ; https://school.js88.com/scl_h/22052630/</t>
+        </is>
+      </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2606,15 +3590,19 @@
           <t>北海道芸術高等学校</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>0135-48-5131</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H54" s="8" t="n"/>
@@ -2626,6 +3614,21 @@
       </c>
       <c r="K54" s="8" t="n"/>
       <c r="L54" s="9" t="n"/>
+      <c r="M54" s="10" t="inlineStr">
+        <is>
+          <t>【所在地注意】本校は2015年に清水町から仁木町へ移転済み。番号は仁木本校のもの</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kyokei.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O54" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2646,15 +3649,19 @@
           <t>北海道栄高等学校</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>0144-82-2185</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H55" s="8" t="n"/>
@@ -2666,6 +3673,21 @@
       </c>
       <c r="K55" s="8" t="n"/>
       <c r="L55" s="9" t="n"/>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>白老町。苫小牧市への移転計画の報道あり（移転後は番号が変わる可能性）</t>
+        </is>
+      </c>
+      <c r="N55" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22053020/</t>
+        </is>
+      </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -2686,15 +3708,19 @@
           <t>北海道文教大学附属高等学校</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>0123-25-5570</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H56" s="8" t="n"/>
@@ -2706,6 +3732,21 @@
       </c>
       <c r="K56" s="8" t="n"/>
       <c r="L56" s="9" t="n"/>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052730</t>
+        </is>
+      </c>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -2726,15 +3767,19 @@
           <t>酪農学園大学附属とわの森三愛高等学校</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>011-386-3111</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>普通科・専門学科</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H57" s="8" t="n"/>
@@ -2746,6 +3791,21 @@
       </c>
       <c r="K57" s="8" t="n"/>
       <c r="L57" s="9" t="n"/>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。通信制課程は011-388-4831</t>
+        </is>
+      </c>
+      <c r="N57" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052750/</t>
+        </is>
+      </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -2766,15 +3826,19 @@
           <t>立命館慶祥高等学校</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>011-381-8888</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H58" s="8" t="n"/>
@@ -2786,6 +3850,21 @@
       </c>
       <c r="K58" s="8" t="n"/>
       <c r="L58" s="9" t="n"/>
+      <c r="M58" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。札幌市立中学校の配布資料と一致</t>
+        </is>
+      </c>
+      <c r="N58" s="11" t="inlineStr">
+        <is>
+          <t>https://www.minkou.jp/junior/school/6019/</t>
+        </is>
+      </c>
+      <c r="O58" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -2806,15 +3885,19 @@
           <t>稚内大谷高等学校</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>0162-32-2660</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>普通科</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>開く</t>
         </is>
       </c>
       <c r="H59" s="8" t="n"/>
@@ -2826,10 +3909,25 @@
       </c>
       <c r="K59" s="8" t="n"/>
       <c r="L59" s="9" t="n"/>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>学校情報サイト1件のみで確認</t>
+        </is>
+      </c>
+      <c r="N59" s="11" t="inlineStr">
+        <is>
+          <t>https://school.js88.com/scl_h/22052960</t>
+        </is>
+      </c>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L59"/>
-  <conditionalFormatting sqref="A5:L59">
+  <autoFilter ref="A4:O59"/>
+  <conditionalFormatting sqref="A5:O59">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -2846,61 +3944,61 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2937,1468 +4035,1468 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>所在地</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>学校数</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>電話番号入力済</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>架電済</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>不在・折返し待ち</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>担当者不在</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>資料送付</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>アポ獲得</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>検討中</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>番号不明</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>函館市</t>
         </is>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A4)</f>
         <v/>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A4,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="16">
         <f>B4-COUNTIFS('架電リスト'!$C$5:$C$59,A4,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A4,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A4,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A4,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A4,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A4,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A4,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A4,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A4,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>旭川市</t>
         </is>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A5)</f>
         <v/>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A5,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="16">
         <f>B5-COUNTIFS('架電リスト'!$C$5:$C$59,A5,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A5,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A5,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A5,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A5,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A5,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A5,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A5,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A5,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>札幌市豊平区</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A6)</f>
         <v/>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A6,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="16">
         <f>B6-COUNTIFS('架電リスト'!$C$5:$C$59,A6,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A6,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A6,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A6,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A6,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A6,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A6,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A6,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A6,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>小樽市</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A7)</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A7,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="16">
         <f>B7-COUNTIFS('架電リスト'!$C$5:$C$59,A7,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A7,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A7,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A7,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A7,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A7,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A7,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A7,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A7,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>札幌市東区</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A8)</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A8,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="16">
         <f>B8-COUNTIFS('架電リスト'!$C$5:$C$59,A8,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A8,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A8,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A8,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A8,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A8,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A8,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A8,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A8,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>札幌市中央区</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A9)</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A9,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="16">
         <f>B9-COUNTIFS('架電リスト'!$C$5:$C$59,A9,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A9,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A9,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A9,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A9,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A9,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A9,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A9,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A9,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>帯広市</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A10)</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A10,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="16">
         <f>B10-COUNTIFS('架電リスト'!$C$5:$C$59,A10,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A10,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A10,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A10,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A10,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A10,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A10,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A10,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K10" s="11">
+      <c r="K10" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A10,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>室蘭市</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A11)</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A11,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="16">
         <f>B11-COUNTIFS('架電リスト'!$C$5:$C$59,A11,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A11,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A11,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A11,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A11,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A11,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A11,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A11,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A11,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>苫小牧市</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A12)</f>
         <v/>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A12,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="16">
         <f>B12-COUNTIFS('架電リスト'!$C$5:$C$59,A12,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A12,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A12,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A12,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A12,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A12,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A12,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A12,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A12,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>札幌市南区</t>
         </is>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A13)</f>
         <v/>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A13,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="16">
         <f>B13-COUNTIFS('架電リスト'!$C$5:$C$59,A13,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A13,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A13,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A13,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A13,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A13,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A13,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A13,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K13" s="11">
+      <c r="K13" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A13,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>札幌市北区</t>
         </is>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A14)</f>
         <v/>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A14,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="16">
         <f>B14-COUNTIFS('架電リスト'!$C$5:$C$59,A14,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A14,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A14,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A14,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A14,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A14,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A14,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A14,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K14" s="11">
+      <c r="K14" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A14,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>江別市</t>
         </is>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A15)</f>
         <v/>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A15,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="16">
         <f>B15-COUNTIFS('架電リスト'!$C$5:$C$59,A15,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A15,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A15,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A15,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A15,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A15,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A15,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A15,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A15,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>北見市</t>
         </is>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A16)</f>
         <v/>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A16,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="16">
         <f>B16-COUNTIFS('架電リスト'!$C$5:$C$59,A16,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A16,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A16,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A16,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A16,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A16,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A16,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A16,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A16,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>深川市</t>
         </is>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A17)</f>
         <v/>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A17,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="16">
         <f>B17-COUNTIFS('架電リスト'!$C$5:$C$59,A17,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A17,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A17,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A17,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A17,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A17,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A17,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A17,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A17,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>和寒町</t>
         </is>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A18)</f>
         <v/>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A18,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="16">
         <f>B18-COUNTIFS('架電リスト'!$C$5:$C$59,A18,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A18,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A18,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A18,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A18,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H18" s="11">
+      <c r="H18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A18,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A18,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A18,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K18" s="11">
+      <c r="K18" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A18,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>北広島市</t>
         </is>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A19)</f>
         <v/>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A19,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="16">
         <f>B19-COUNTIFS('架電リスト'!$C$5:$C$59,A19,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A19,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A19,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A19,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A19,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A19,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A19,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A19,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K19" s="11">
+      <c r="K19" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A19,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>札幌市西区</t>
         </is>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A20)</f>
         <v/>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A20,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="16">
         <f>B20-COUNTIFS('架電リスト'!$C$5:$C$59,A20,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A20,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A20,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A20,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A20,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A20,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A20,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A20,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A20,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>芽室町</t>
         </is>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A21)</f>
         <v/>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A21,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="16">
         <f>B21-COUNTIFS('架電リスト'!$C$5:$C$59,A21,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A21,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A21,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A21,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A21,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A21,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A21,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A21,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A21,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>芦別市</t>
         </is>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A22)</f>
         <v/>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A22,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="16">
         <f>B22-COUNTIFS('架電リスト'!$C$5:$C$59,A22,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A22,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A22,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A22,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A22,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A22,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A22,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A22,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A22,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>千歳市</t>
         </is>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A23)</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A23,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="16">
         <f>B23-COUNTIFS('架電リスト'!$C$5:$C$59,A23,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A23,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A23,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A23,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A23,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A23,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A23,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A23,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K23" s="11">
+      <c r="K23" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A23,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>釧路市</t>
         </is>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A24)</f>
         <v/>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A24,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="16">
         <f>B24-COUNTIFS('架電リスト'!$C$5:$C$59,A24,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A24,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A24,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A24,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A24,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A24,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A24,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A24,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K24" s="11">
+      <c r="K24" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A24,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>札幌市厚別区</t>
         </is>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A25)</f>
         <v/>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A25,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="16">
         <f>B25-COUNTIFS('架電リスト'!$C$5:$C$59,A25,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A25,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A25,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A25,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A25,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A25,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A25,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A25,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A25,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>余市町</t>
         </is>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A26)</f>
         <v/>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A26,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="16">
         <f>B26-COUNTIFS('架電リスト'!$C$5:$C$59,A26,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A26,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A26,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A26,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A26,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A26,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A26,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A26,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K26" s="11">
+      <c r="K26" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A26,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>札幌市清田区</t>
         </is>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A27)</f>
         <v/>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A27,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="16">
         <f>B27-COUNTIFS('架電リスト'!$C$5:$C$59,A27,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A27,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A27,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A27,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A27,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A27,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A27,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A27,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K27" s="11">
+      <c r="K27" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A27,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>札幌市手稲区</t>
         </is>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A28)</f>
         <v/>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A28,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="16">
         <f>B28-COUNTIFS('架電リスト'!$C$5:$C$59,A28,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A28,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A28,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A28,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A28,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A28,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A28,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A28,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K28" s="11">
+      <c r="K28" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A28,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>清水町</t>
         </is>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A29)</f>
         <v/>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A29,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="16">
         <f>B29-COUNTIFS('架電リスト'!$C$5:$C$59,A29,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A29,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A29,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A29,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A29,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A29,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A29,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A29,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K29" s="11">
+      <c r="K29" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A29,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>白老町</t>
         </is>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A30)</f>
         <v/>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A30,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="16">
         <f>B30-COUNTIFS('架電リスト'!$C$5:$C$59,A30,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A30,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A30,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A30,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A30,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A30,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A30,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A30,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K30" s="11">
+      <c r="K30" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A30,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>恵庭市</t>
         </is>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A31)</f>
         <v/>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A31,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="16">
         <f>B31-COUNTIFS('架電リスト'!$C$5:$C$59,A31,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A31,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A31,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A31,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A31,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A31,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A31,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A31,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K31" s="11">
+      <c r="K31" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A31,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>稚内市</t>
         </is>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="16">
         <f>COUNTIF('架電リスト'!$C$5:$C$59,A32)</f>
         <v/>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,A32,'架電リスト'!$E$5:$E$59,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="16">
         <f>B32-COUNTIFS('架電リスト'!$C$5:$C$59,A32,'架電リスト'!$J$5:$J$59,"未架電")-COUNTIFS('架電リスト'!$C$5:$C$59,A32,'架電リスト'!$J$5:$J$59,"")</f>
         <v/>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A32,'架電リスト'!$J$5:$J$59,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A32,'架電リスト'!$J$5:$J$59,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A32,'架電リスト'!$J$5:$J$59,"資料送付")</f>
         <v/>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A32,'架電リスト'!$J$5:$J$59,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A32,'架電リスト'!$J$5:$J$59,"検討中")</f>
         <v/>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A32,'架電リスト'!$J$5:$J$59,"NG")</f>
         <v/>
       </c>
-      <c r="K32" s="11">
+      <c r="K32" s="16">
         <f>COUNTIFS('架電リスト'!$C$5:$C$59,$A32,'架電リスト'!$J$5:$J$59,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="17">
         <f>SUM(B4:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="17">
         <f>SUM(C4:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="17">
         <f>SUM(D4:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="17">
         <f>SUM(E4:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="17">
         <f>SUM(F4:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="17">
         <f>SUM(G4:G32)</f>
         <v/>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="17">
         <f>SUM(H4:H32)</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="17">
         <f>SUM(I4:I32)</f>
         <v/>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="17">
         <f>SUM(J4:J32)</f>
         <v/>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="17">
         <f>SUM(K4:K32)</f>
         <v/>
       </c>
@@ -4414,87 +5512,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>■ 使い方</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>・「架電リスト」の黄色の列（電話番号・架電日・担当者・架電結果・次回連絡日・メモ）に入力してください。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>・架電結果はプルダウンから選択します（アポ獲得＝緑、NG＝グレーで行が自動着色）。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>・「学校情報ページ」の「開く」をクリックすると、学校ネットの各校ページが開きます。電話番号の確認にご利用ください。</t>
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>・「学校情報ページ」の「開く」をクリックすると、学校ネットの各校ページが開きます。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>・「番号の確度」：高＝公式サイト、または2つ以上の情報源で一致／中＝情報サイト1件のみで確認／低・要調査＝特定できず。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>・「電話番号の補足」に、代表番号の共有・別番号（入試事務局など）・移転などの注意を記載しています。架電前にご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>・市区町村で絞り込む場合は、見出し行「所在地（市区町村）」の▼（フィルター）を使用してください。</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>・「市区町村別集計」は入力内容に連動して自動で集計されます（学校数の多い順）。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>■ 元データについての注意</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・北海道、55校）の貼り付けデータ。並び順は元データの掲載順です。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>・元データには電話番号の記載がないため、電話番号欄は空欄です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>・電話番号は元データに記載がないため、2026年10月にWeb検索（学校公式サイト、JS日本の学校、みんなの高校情報、自治体・ハローワーク・道私学協会の資料など）で調査しました。推測による補完はしていません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>・クラーク記念国際・星槎国際など広域通信制の学校は、所在地が本校のみの表記です。架電先（本校／各キャンパス）にご注意ください。</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>・閉校・統合・校名変更などは反映されていない可能性があります。架電前にご確認ください。</t>
         </is>

--- a/call-list/私立高校_架電リスト_北海道.xlsx
+++ b/call-list/私立高校_架電リスト_北海道.xlsx
@@ -603,7 +603,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出典：学校ネット 私立高校検索結果（ご提供の貼り付けデータ）。電話番号は2026年10月にWeb検索で調査（出典・確度はM〜N列）。架電前に「確度：中・低」の番号は念のためご確認ください。</t>
+          <t>出典：学校ネット 私立高校検索結果（ご提供の貼り付けデータ）。電話番号は2026年10月にWeb検索で調査（確度はF列、出典はN列）。架電前に「確度：中・低」の番号は念のためご確認ください。</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>・クラーク記念国際・星槎国際など広域通信制の学校は、所在地が本校のみの表記です。架電先（本校／各キャンパス）にご注意ください。</t>
+          <t>・通信制（広域通信制）の学校は、所在地・電話番号とも本校のものです。架電先（本校／各キャンパス）にご注意ください。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_北海道.xlsx
+++ b/call-list/私立高校_架電リスト_北海道.xlsx
@@ -5549,7 +5549,7 @@
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>・「番号の確度」：高＝公式サイト、または2つ以上の情報源で一致／中＝情報サイト1件のみで確認／低・要調査＝特定できず。</t>
+          <t>・「番号の確度」：高＝公式サイト、または2つ以上の情報源で一致／中＝情報サイト1件のみ、または代表番号と断定できず（補足欄参照）／低・要調査＝特定できず。</t>
         </is>
       </c>
     </row>
@@ -5563,14 +5563,14 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>・市区町村で絞り込む場合は、見出し行「所在地（市区町村）」の▼（フィルター）を使用してください。</t>
+          <t>・都道府県や市区町村で絞り込む場合は、見出し行の▼（フィルター）を使用してください。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>・「市区町村別集計」は入力内容に連動して自動で集計されます（学校数の多い順）。</t>
+          <t>・集計シートは入力内容に連動して自動で集計されます。</t>
         </is>
       </c>
     </row>
@@ -5587,14 +5587,14 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・北海道、55校）の貼り付けデータ。並び順は元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・北海道、55校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>・電話番号は元データに記載がないため、2026年10月にWeb検索（学校公式サイト、JS日本の学校、みんなの高校情報、自治体・ハローワーク・道私学協会の資料など）で調査しました。推測による補完はしていません。</t>
+          <t>・電話番号は元データに記載がないため、2026年10月にWeb検索（学校公式サイト、JS日本の学校、みんなの高校情報、自治体・ハローワーク・各道県の私学協会の資料など）で調査しました。推測による補完はしていません。</t>
         </is>
       </c>
     </row>
